--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484588_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484588_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0584</v>
+        <v>7.2458</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7054</v>
+        <v>6.7194</v>
       </c>
       <c r="F2" t="n">
-        <v>0.353</v>
+        <v>0.5264</v>
       </c>
       <c r="G2" t="n">
         <v>5.2327</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7449</v>
+        <v>-0.5575</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0015</v>
+        <v>0.0125</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.57</v>
       </c>
       <c r="V2" t="n">
         <v>1.2878</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1831</v>
+        <v>6.7195</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2407</v>
+        <v>6.6532</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0576</v>
+        <v>0.0663</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1429</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6686</v>
+        <v>-0.1322</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8808</v>
+        <v>-0.4683</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2123</v>
+        <v>0.3361</v>
       </c>
       <c r="V3" t="n">
         <v>6.3453</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3364</v>
+        <v>6.12</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9022</v>
+        <v>3.438</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4342</v>
+        <v>2.6819</v>
       </c>
       <c r="G4" t="n">
         <v>3.9139</v>
@@ -766,13 +766,13 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4284</v>
+        <v>-0.6448</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5324</v>
+        <v>0.0034</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8959</v>
+        <v>-0.6482</v>
       </c>
       <c r="V4" t="n">
         <v>1.5681</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6491</v>
+        <v>5.0229</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7639</v>
+        <v>2.1624</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8853</v>
+        <v>2.8605</v>
       </c>
       <c r="G5" t="n">
         <v>5.1693</v>
@@ -844,13 +844,13 @@
         <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5097</v>
+        <v>-0.136</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6056</v>
+        <v>-0.207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0958</v>
+        <v>0.0711</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0104</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0485</v>
+        <v>1.3718</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0584</v>
+        <v>0.5528</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1069</v>
+        <v>0.819</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0584</v>
+        <v>2.5239</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6325</v>
+        <v>2.2611</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5741</v>
+        <v>0.2628</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0983</v>
+        <v>3.0724</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0588</v>
+        <v>1.6873</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.157</v>
+        <v>1.3851</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1567</v>
+        <v>-0.5486</v>
       </c>
       <c r="N6" t="n">
         <v>0.5738</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.417</v>
+        <v>-1.1223</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0346</v>
+        <v>-0.741</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5113</v>
+        <v>-0.0927</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5233</v>
+        <v>-0.6482</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2774</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7888</v>
+        <v>1.2591</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9349</v>
+        <v>2.3308</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1461</v>
+        <v>-1.0718</v>
       </c>
       <c r="G7" t="n">
         <v>-0.07439999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0752</v>
+        <v>0.5454</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8416</v>
+        <v>0.2376</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2335</v>
+        <v>0.3079</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3115</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5303</v>
+        <v>1.0284</v>
       </c>
       <c r="E8" t="n">
-        <v>0.058</v>
+        <v>-1.3601</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4722</v>
+        <v>2.3884</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5239</v>
+        <v>0.0584</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2611</v>
+        <v>1.6325</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2628</v>
+        <v>-1.5741</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0724</v>
+        <v>-0.0983</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6873</v>
+        <v>1.0588</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3851</v>
+        <v>-1.157</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5486</v>
+        <v>0.1567</v>
       </c>
       <c r="N8" t="n">
         <v>0.5738</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1223</v>
+        <v>-0.417</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5825</v>
+        <v>1.0145</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5875</v>
+        <v>0.2097</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.995</v>
+        <v>0.8048</v>
       </c>
       <c r="V8" t="n">
         <v>0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>1.2774</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0122</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5913</v>
+        <v>-0.4951</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5817</v>
+        <v>0.5073</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4186</v>
@@ -1156,13 +1156,13 @@
         <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3241</v>
+        <v>-0.3022</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0369</v>
+        <v>0.0592</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2871</v>
+        <v>-0.3614</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CARPIO MANEZ</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2167</v>
+        <v>-0.1401</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.8449</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2167</v>
+        <v>0.7048</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0885</v>
+        <v>-1.6522</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0885</v>
+        <v>0.3574</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-2.0096</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4552</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.2722</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0885</v>
+        <v>-0.8351</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0885</v>
+        <v>-0.0977</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1282</v>
+        <v>0.2293</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.0279</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1282</v>
+        <v>0.2572</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>J. CARPIO MANEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6958</v>
+        <v>-0.2167</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2024</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5066000000000001</v>
+        <v>-0.2167</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6522</v>
+        <v>-0.0885</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3574</v>
+        <v>-0.0885</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0096</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8169999999999999</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4552</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2722</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8351</v>
+        <v>-0.0885</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0977</v>
+        <v>-0.0885</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3264</v>
+        <v>-0.1282</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3854</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.059</v>
+        <v>-0.1282</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0947</v>
+        <v>-2.5456</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4044</v>
+        <v>-0.5828</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6903</v>
+        <v>-1.9628</v>
       </c>
       <c r="G12" t="n">
         <v>0.133</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2225</v>
+        <v>-0.2283</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2187</v>
+        <v>0.0404</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0038</v>
+        <v>-0.2687</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9005</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7991</v>
+        <v>-2.7222</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4133</v>
+        <v>-3.2621</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6142</v>
+        <v>0.5399</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6138</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0858</v>
+        <v>-0.0089</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3854</v>
+        <v>-0.2342</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2996</v>
+        <v>0.2253</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.7787</v>
+        <v>23.1551</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9353</v>
+        <v>15.3116</v>
       </c>
       <c r="F14" t="n">
-        <v>7.843400000000002</v>
+        <v>7.843200000000002</v>
       </c>
       <c r="G14" t="n">
         <v>12.0408</v>
@@ -1546,13 +1546,13 @@
         <v>17.4093</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4663</v>
+        <v>-1.0899</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8439</v>
+        <v>-0.4672999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6222999999999997</v>
+        <v>-0.6222999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>7.622599999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9711</v>
+        <v>0.9959</v>
       </c>
       <c r="E15" t="n">
         <v>1.2369</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2658</v>
+        <v>-0.241</v>
       </c>
       <c r="G15" t="n">
         <v>1.7162</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4232</v>
+        <v>-0.3984</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3681</v>
+        <v>-0.3433</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3219</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>I. EGIDO MUÑOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.675</v>
+        <v>0.6251</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2607</v>
+        <v>0.6251</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5857</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3023</v>
+        <v>0.6251</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.203</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0993</v>
+        <v>0.6251</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8302</v>
+        <v>0.6251</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5445</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2857</v>
+        <v>0.6251</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1324</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7475</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3849</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4879</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2685</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2194</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. EGIDO MUÑOZ</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6251</v>
+        <v>-0.2547</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6251</v>
+        <v>1.2973</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-1.552</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6251</v>
+        <v>1.4492</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1319</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6251</v>
+        <v>1.3174</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6251</v>
+        <v>2.6966</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.1547</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6251</v>
+        <v>1.5419</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.2474</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.0228</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.2246</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2983</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.483</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1847</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1585</v>
+        <v>-0.5182</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3935</v>
+        <v>0.9145</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.552</v>
+        <v>-1.4327</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4492</v>
+        <v>-2.3023</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1319</v>
+        <v>-2.203</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3174</v>
+        <v>-0.0993</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6966</v>
+        <v>0.8302</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1547</v>
+        <v>0.5445</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5419</v>
+        <v>0.2857</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2474</v>
+        <v>-3.1324</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0228</v>
+        <v>-2.7475</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2246</v>
+        <v>-0.3849</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2021</v>
+        <v>1.2947</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3869</v>
+        <v>0.9224</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1847</v>
+        <v>0.3723</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5889</v>
+        <v>1.5889</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2294</v>
+        <v>-0.9115</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9356</v>
+        <v>-0.5461</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2938</v>
+        <v>-0.3655</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8159</v>
+        <v>1.5049</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6108</v>
+        <v>-0.2006</v>
       </c>
       <c r="I19" t="n">
-        <v>0.795</v>
+        <v>1.7055</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1913</v>
+        <v>2.5338</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8581</v>
+        <v>0.5077</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6667999999999999</v>
+        <v>2.0261</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3754</v>
+        <v>-1.029</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2472</v>
+        <v>-0.7083</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1282</v>
+        <v>-0.3207</v>
       </c>
       <c r="P19" t="n">
-        <v>0.733</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R19" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1204</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2557</v>
+        <v>-0.3311</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1353</v>
+        <v>0.3948</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.267</v>
+        <v>-0.8308</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>-0.8308</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>J. CLIMENT GOMIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5439</v>
+        <v>-1.22</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9307</v>
+        <v>0.2145</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6132</v>
+        <v>-1.4345</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5049</v>
+        <v>-1.4036</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2006</v>
+        <v>-4.1191</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7055</v>
+        <v>2.7155</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5338</v>
+        <v>0.4054</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5077</v>
+        <v>-2.4065</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0261</v>
+        <v>2.8119</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.029</v>
+        <v>-1.8091</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7083</v>
+        <v>-1.7127</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3207</v>
+        <v>-0.0964</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5686</v>
+        <v>0.4664</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7157</v>
+        <v>0.3643</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1471</v>
+        <v>0.1022</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8308</v>
+        <v>0.6335</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8308</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CLIMENT GOMIS</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7824</v>
+        <v>-1.2908</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1701</v>
+        <v>1.3047</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6122</v>
+        <v>-2.5955</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4036</v>
+        <v>-1.0775</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.1191</v>
+        <v>-1.2986</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7155</v>
+        <v>0.2211</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4054</v>
+        <v>0.9145</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4065</v>
+        <v>0.7895</v>
       </c>
       <c r="L21" t="n">
-        <v>2.8119</v>
+        <v>0.125</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8091</v>
+        <v>-1.992</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7127</v>
+        <v>-2.0881</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0964</v>
+        <v>0.0961</v>
       </c>
       <c r="P21" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0959</v>
+        <v>0.6908</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0203</v>
+        <v>0.3511</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0756</v>
+        <v>0.3397</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6335</v>
+        <v>-1.4539</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2774</v>
+        <v>0.9554</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6439</v>
+        <v>-2.4093</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2349</v>
+        <v>-1.4188</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4393</v>
+        <v>-1.2241</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6742</v>
+        <v>-0.1947</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0775</v>
+        <v>-0.8159</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2986</v>
+        <v>-1.6108</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2211</v>
+        <v>0.795</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9145</v>
+        <v>-1.1913</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7895</v>
+        <v>-1.8581</v>
       </c>
       <c r="L22" t="n">
-        <v>0.125</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.992</v>
+        <v>0.3754</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0881</v>
+        <v>0.2472</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0961</v>
+        <v>0.1282</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2532</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5143</v>
+        <v>-0.0328</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2611</v>
+        <v>-0.0362</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4539</v>
+        <v>-1.267</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4093</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3756</v>
+        <v>-2.1512</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.757</v>
+        <v>-1.6608</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6186</v>
+        <v>-0.4904</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7073</v>
@@ -2248,13 +2248,13 @@
         <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.1505</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1297</v>
+        <v>-0.0335</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0558</v>
+        <v>0.184</v>
       </c>
       <c r="V23" t="n">
         <v>0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6156</v>
+        <v>-2.6462</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3236</v>
+        <v>-2.1312</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.292</v>
+        <v>-0.515</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1761</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1085</v>
+        <v>0.0779</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5505</v>
+        <v>-0.3582</v>
       </c>
       <c r="U24" t="n">
-        <v>0.659</v>
+        <v>0.4361</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4643</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8249</v>
+        <v>-5.3116</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9313</v>
+        <v>-2.2198</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8936</v>
+        <v>-3.0918</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1885</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7284</v>
+        <v>0.2417</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1252</v>
+        <v>-0.1632</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6031</v>
+        <v>0.405</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7313</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.2848</v>
+        <v>-7.0357</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.7506</v>
+        <v>-5.6544</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5342</v>
+        <v>-1.3813</v>
       </c>
       <c r="G26" t="n">
         <v>-4.665</v>
@@ -2482,13 +2482,13 @@
         <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>0.638</v>
+        <v>0.8871</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3454</v>
+        <v>0.4416</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2925</v>
+        <v>0.4455</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5089</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.7788</v>
+        <v>-21.1377</v>
       </c>
       <c r="E27" t="n">
         <v>-7.8434</v>
       </c>
       <c r="F27" t="n">
-        <v>-13.9353</v>
+        <v>-13.2944</v>
       </c>
       <c r="G27" t="n">
         <v>-12.0408</v>
@@ -2539,7 +2539,7 @@
         <v>-3.8606</v>
       </c>
       <c r="L27" t="n">
-        <v>8.016500000000001</v>
+        <v>8.016500000000002</v>
       </c>
       <c r="M27" t="n">
         <v>-16.197</v>
@@ -2560,16 +2560,16 @@
         <v>12.828</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4663</v>
+        <v>3.1071</v>
       </c>
       <c r="T27" t="n">
-        <v>0.6223000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8437</v>
+        <v>2.4848</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.6227</v>
+        <v>-7.622699999999999</v>
       </c>
       <c r="W27" t="n">
         <v>4.787500000000001</v>
